--- a/游戏设计王/捕鱼游戏数学-PartI-击杀率模型.xlsx
+++ b/游戏设计王/捕鱼游戏数学-PartI-击杀率模型.xlsx
@@ -265,13 +265,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.000%"/>
     <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="178" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -962,7 +963,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1030,6 +1031,11 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1750,7 +1756,7 @@
       <c r="B6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="42">
         <f>IF(OR(C4="",C4=0),"",C5/C4)</f>
         <v>0.009</v>
       </c>
@@ -2031,15 +2037,15 @@
       <c r="C17" s="9">
         <v>100</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="42">
         <f>IF(OR(C17="",C17=0),"",$C$15/C17)</f>
         <v>0.009</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="42">
         <f>IF(OR(D17="",$C$14="",$C$14=0),"",D17/$C$14)</f>
         <v>0.003</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="45">
         <f>IF(OR(E17="",C17=""),"",C17*E17)</f>
         <v>0.3</v>
       </c>
@@ -2060,15 +2066,15 @@
       <c r="C18" s="9">
         <v>100</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="42">
         <f>IF(OR(C18="",C18=0),"",$C$15/C18)</f>
         <v>0.009</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="42">
         <f>IF(OR(D18="",$C$14="",$C$14=0),"",D18/$C$14)</f>
         <v>0.003</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="45">
         <f>IF(OR(E18="",C18=""),"",C18*E18)</f>
         <v>0.3</v>
       </c>
@@ -2089,15 +2095,15 @@
       <c r="C19" s="9">
         <v>100</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="42">
         <f>IF(OR(C19="",C19=0),"",$C$15/C19)</f>
         <v>0.009</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="42">
         <f>IF(OR(D19="",$C$14="",$C$14=0),"",D19/$C$14)</f>
         <v>0.003</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="45">
         <f>IF(OR(E19="",C19=""),"",C19*E19)</f>
         <v>0.3</v>
       </c>
@@ -2116,15 +2122,15 @@
         <v>63</v>
       </c>
       <c r="C20" s="8"/>
-      <c r="D20" s="11" t="str">
+      <c r="D20" s="42" t="str">
         <f>IF(OR(C20="",C20=0),"",$C$15/C20)</f>
         <v/>
       </c>
-      <c r="E20" s="11" t="str">
+      <c r="E20" s="42" t="str">
         <f>IF(OR(D20="",$C$14="",$C$14=0),"",D20/$C$14)</f>
         <v/>
       </c>
-      <c r="F20" s="20" t="str">
+      <c r="F20" s="45" t="str">
         <f>IF(OR(E20="",C20=""),"",C20*E20)</f>
         <v/>
       </c>
@@ -2143,15 +2149,15 @@
         <v>65</v>
       </c>
       <c r="C21" s="8"/>
-      <c r="D21" s="11" t="str">
+      <c r="D21" s="42" t="str">
         <f>IF(OR(C21="",C21=0),"",$C$15/C21)</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="str">
+      <c r="E21" s="42" t="str">
         <f>IF(OR(D21="",$C$14="",$C$14=0),"",D21/$C$14)</f>
         <v/>
       </c>
-      <c r="F21" s="20" t="str">
+      <c r="F21" s="45" t="str">
         <f>IF(OR(E21="",C21=""),"",C21*E21)</f>
         <v/>
       </c>
@@ -2178,7 +2184,7 @@
       <c r="E22" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="45">
         <f>SUM(F17:F21)</f>
         <v>0.9</v>
       </c>
